--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_6_ablation_and_lag_resolution_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_6_ablation_and_lag_resolution_source_data.xlsx
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1060405643738977</v>
+        <v>-0.1314247921390779</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1238201910666887</v>
+        <v>-0.1652787585622485</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08857173906574164</v>
+        <v>-0.1035211143280841</v>
       </c>
       <c r="G2" t="n">
         <v>126</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04617031997984389</v>
+        <v>-0.03165154950869242</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06969029681318213</v>
+        <v>-0.05451654632441212</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02304807692307687</v>
+        <v>-0.01316184164519924</v>
       </c>
       <c r="G3" t="n">
         <v>126</v>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05165028974552788</v>
+        <v>0.03470647518266567</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03164712126494166</v>
+        <v>0.02040816326530615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07131937064188189</v>
+        <v>0.04884362576707391</v>
       </c>
       <c r="G4" t="n">
         <v>126</v>
@@ -604,13 +604,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.009101788863693616</v>
+        <v>0.01319601914839996</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0270030699688933</v>
+        <v>-0.002996376629695844</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01177854906242313</v>
+        <v>0.0259219430154333</v>
       </c>
       <c r="G5" t="n">
         <v>126</v>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.0007243638196018365</v>
+        <v>-0.0003464348702444386</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001344544120707608</v>
+        <v>-0.001449403290728135</v>
       </c>
       <c r="F6" t="n">
-        <v>3.117024003419218e-05</v>
+        <v>0.0001131303144055795</v>
       </c>
       <c r="G6" t="n">
         <v>126</v>
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01817208364827416</v>
+        <v>-0.04462711010330067</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0369359851933749</v>
+        <v>-0.07216803775916526</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.002217297925638767</v>
+        <v>-0.01804815669342529</v>
       </c>
       <c r="G7" t="n">
         <v>126</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04075333837238604</v>
+        <v>-0.01325900730662644</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0667327772733456</v>
+        <v>-0.02735487528344671</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01579835390218514</v>
+        <v>0.004672406462585078</v>
       </c>
       <c r="G8" t="n">
         <v>126</v>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.003779289493575311</v>
+        <v>-0.003369866465104621</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02805312953368128</v>
+        <v>-0.01423094837063351</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01664418819444458</v>
+        <v>0.008063518636621468</v>
       </c>
       <c r="G9" t="n">
         <v>126</v>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01565255731922399</v>
+        <v>0.007684555303602902</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03104086387804045</v>
+        <v>-0.006517057188612942</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001821854958677564</v>
+        <v>0.02311882933320372</v>
       </c>
       <c r="G10" t="n">
         <v>126</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.448223733932171e-05</v>
+        <v>-3.149407911318125e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0006580388735398568</v>
+        <v>-0.0006349363274720743</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0007215589635020582</v>
+        <v>0.0003393748748088147</v>
       </c>
       <c r="G11" t="n">
         <v>126</v>
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1170634920634923</v>
+        <v>-0.1444318468127992</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.140217801674427</v>
+        <v>-0.1806396087846904</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09283666203252805</v>
+        <v>-0.108108224551023</v>
       </c>
       <c r="G12" t="n">
         <v>126</v>
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03546233308138058</v>
+        <v>0.04084782060972536</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01634594245836643</v>
+        <v>0.02412512888020266</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05561350033608699</v>
+        <v>0.06457335511920999</v>
       </c>
       <c r="G13" t="n">
         <v>126</v>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.009448223733938055</v>
+        <v>-0.02658100277147901</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04412434218142063</v>
+        <v>-0.05156995927622735</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01524562715470714</v>
+        <v>-0.008147360796170325</v>
       </c>
       <c r="G14" t="n">
         <v>126</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.004913076341647726</v>
+        <v>0.01105442176870752</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008168095405156528</v>
+        <v>-0.006408963367481953</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02114507030601484</v>
+        <v>0.0252317522597274</v>
       </c>
       <c r="G15" t="n">
         <v>126</v>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.0003149407911312574</v>
+        <v>-0.0001574703955655732</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0002473386291129864</v>
+        <v>-0.0005869060574367646</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001216335605491531</v>
+        <v>0.00028247081788563</v>
       </c>
       <c r="G16" t="n">
         <v>126</v>
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07561728395061723</v>
+        <v>-0.06610607205845298</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09652157658680781</v>
+        <v>-0.08916710512329938</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06033323917802415</v>
+        <v>-0.0533064333766748</v>
       </c>
       <c r="G17" t="n">
         <v>126</v>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01455026455026465</v>
+        <v>0.01338498362307872</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006817812547083771</v>
+        <v>0.007626454721322004</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0201492007102864</v>
+        <v>0.01877466745393136</v>
       </c>
       <c r="G18" t="n">
         <v>126</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03228143109095494</v>
+        <v>0.01716427311665403</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02011404804309412</v>
+        <v>0.007590073066263578</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04522790701865565</v>
+        <v>0.02341292960192171</v>
       </c>
       <c r="G19" t="n">
         <v>126</v>
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.008849836230788721</v>
+        <v>0.006141345427059686</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001697312012692806</v>
+        <v>-0.005560261788538874</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0186512170881806</v>
+        <v>0.01235964974224985</v>
       </c>
       <c r="G20" t="n">
         <v>126</v>
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.0003464348702444386</v>
+        <v>-0.0003779289493575089</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0004101553436716587</v>
+        <v>-0.001020975056689355</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00114773243771407</v>
+        <v>0.0001477948237821129</v>
       </c>
       <c r="G21" t="n">
         <v>126</v>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.0553352559480894</v>
+        <v>0.03785254824344384</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.000784126541083688</v>
+        <v>-0.01489631006864989</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.09613041098084089</v>
       </c>
       <c r="G22" t="n">
         <v>126</v>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.08406432748538012</v>
+        <v>0.06110836219693221</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02347223383500557</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1587474120082815</v>
+        <v>0.1098091069917564</v>
       </c>
       <c r="G23" t="n">
         <v>126</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.0131578947368421</v>
+        <v>-0.02160561526650581</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.03798685491723466</v>
+        <v>-0.04465567157768485</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.0131578947368421</v>
+        <v>-0.0009870585654748812</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.03658536585365853</v>
+        <v>-0.02532907644729157</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.03215147020396868</v>
       </c>
       <c r="G25" t="n">
         <v>126</v>
